--- a/Output/robustness.xlsx
+++ b/Output/robustness.xlsx
@@ -418,22 +418,22 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.01987143426751635</v>
+        <v>0.01987123247152484</v>
       </c>
       <c r="E2">
-        <v>0.004961787724162165</v>
+        <v>0.004961789114915679</v>
       </c>
       <c r="F2">
-        <v>4.004894076937117</v>
+        <v>4.004852284388658</v>
       </c>
       <c r="G2">
-        <v>6.204527671571261E-05</v>
+        <v>6.205624685957044E-05</v>
       </c>
       <c r="H2">
-        <v>0.01014650902922555</v>
+        <v>0.01014630450740724</v>
       </c>
       <c r="I2">
-        <v>0.02959635950580716</v>
+        <v>0.02959616043564244</v>
       </c>
     </row>
     <row r="3">
@@ -628,22 +628,22 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.04947352423294215</v>
+        <v>0.04957281677095193</v>
       </c>
       <c r="E8">
-        <v>0.006645543852715086</v>
+        <v>0.006645704763297719</v>
       </c>
       <c r="F8">
-        <v>7.44461632176716</v>
+        <v>7.459376926391325</v>
       </c>
       <c r="G8">
-        <v>9.722657216075414E-14</v>
+        <v>8.693258761586841E-14</v>
       </c>
       <c r="H8">
-        <v>0.03644849762393903</v>
+        <v>0.03654747478300212</v>
       </c>
       <c r="I8">
-        <v>0.06249855084194527</v>
+        <v>0.06259815875890173</v>
       </c>
     </row>
     <row r="9">
@@ -838,22 +838,22 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.0050118114917662</v>
+        <v>0.005011857513695142</v>
       </c>
       <c r="E14">
-        <v>0.003229747794481636</v>
+        <v>0.00322974773983021</v>
       </c>
       <c r="F14">
-        <v>1.551765589972507</v>
+        <v>1.551779865618427</v>
       </c>
       <c r="G14">
-        <v>0.1207183221815232</v>
+        <v>0.1207149051768156</v>
       </c>
       <c r="H14">
-        <v>-0.001318377864565477</v>
+        <v>-0.001318331735521709</v>
       </c>
       <c r="I14">
-        <v>0.01134200084809788</v>
+        <v>0.01134204676291199</v>
       </c>
     </row>
     <row r="15">
